--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8001D00C-7874-420C-9B59-AC96B26FA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC54560-18B7-4B84-AAD1-5208BAA3F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Key</t>
   </si>
@@ -122,6 +122,192 @@
   </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>获得 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 点格挡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>蓄力猛击，造成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 点伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>连续攻击 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 次，每次造成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 点伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>施加 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 层 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{1}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>自身获得 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 层 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{1}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>造成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -129,7 +315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +337,32 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -671,7 +883,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
@@ -705,7 +917,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>28</v>
       </c>
       <c r="B3" t="s">
@@ -734,6 +946,9 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -748,6 +963,9 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -762,6 +980,9 @@
       <c r="D6" t="s">
         <v>24</v>
       </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -776,6 +997,9 @@
       <c r="D7" t="s">
         <v>25</v>
       </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -790,6 +1014,9 @@
       <c r="D8" t="s">
         <v>26</v>
       </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -803,6 +1030,9 @@
       </c>
       <c r="D9" t="s">
         <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC54560-18B7-4B84-AAD1-5208BAA3F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E477574-5B60-4F92-83CB-98D0C69C9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,10 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
-  <si>
-    <t>Key</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -51,9 +48,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>资源标识</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -70,210 +64,10 @@
   </si>
   <si>
     <t>Attack</t>
-  </si>
-  <si>
-    <t>defend</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>strong_attack</t>
-  </si>
-  <si>
-    <t>蓄力攻击</t>
-  </si>
-  <si>
-    <t>multi_attack</t>
-  </si>
-  <si>
-    <t>多段攻击</t>
-  </si>
-  <si>
-    <t>apply_debuff</t>
-  </si>
-  <si>
-    <t>施加减益</t>
-  </si>
-  <si>
-    <t>self_buff</t>
-  </si>
-  <si>
-    <t>自我强化</t>
-  </si>
-  <si>
-    <t>Defend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StrongAttack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MultiAttack</t>
-  </si>
-  <si>
-    <t>Debuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>获得 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 点格挡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>蓄力猛击，造成 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 点伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>连续攻击 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 次，每次造成 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{1}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 点伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>施加 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 层 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{1}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>自身获得 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 层 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{1}</t>
-    </r>
   </si>
   <si>
     <r>
@@ -310,12 +104,36 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>缩小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrinker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害减少30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,12 +155,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -874,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -884,70 +696,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,84 +767,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E477574-5B60-4F92-83CB-98D0C69C9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9FA47F-9B25-47B8-A40E-ACFDF4FEFCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,10 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>shrinker</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,7 +121,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击伤害减少30%</t>
+    <t>shrink_power</t>
+  </si>
+  <si>
+    <t>给予缩小debuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -699,7 +698,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -733,7 +732,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -750,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9FA47F-9B25-47B8-A40E-ACFDF4FEFCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB83055-28BB-4D08-A2E5-FC717FD036A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>缩小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -117,14 +113,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Buff</t>
+    <t>Debuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>shrink_power</t>
-  </si>
-  <si>
-    <t>给予缩小debuff</t>
+    <t>debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负面效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对玩家施加负面效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +699,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -732,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -749,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB83055-28BB-4D08-A2E5-FC717FD036A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800724C3-BFFC-4972-9702-E030C798510F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -70,8 +70,48 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负面效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对玩家施加负面效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策略(状态)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status_card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusCard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>往玩家弃牌堆添加状态牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t>造成 </t>
+      <t>对玩家造成</t>
     </r>
     <r>
       <rPr>
@@ -86,16 +126,6 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
@@ -105,27 +135,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Debuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>debuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负面效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对玩家施加负面效果</t>
+    <t>强化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对自己添加正面效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,7 +155,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,13 +188,6 @@
       <sz val="9"/>
       <color rgb="FF0F1115"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -686,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -698,8 +713,8 @@
       <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
+      <c r="B1" t="s">
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -732,8 +747,8 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="B3" t="s">
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -749,17 +764,17 @@
       <c r="A4">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -775,12 +790,49 @@
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C6" r:id="rId1" tooltip="策略(状态)" display="https://sts2.huijiwiki.com/wiki/%E7%AD%96%E7%95%A5(%E7%8A%B6%E6%80%81)" xr:uid="{2EE2F399-C7DA-419F-A3DF-BB5694AB8488}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>